--- a/Backtest/07-06-21/S&P500stock_07-06-21period252RS90.xlsx
+++ b/Backtest/07-06-21/S&P500stock_07-06-21period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="85">
   <si>
     <t>Stock</t>
   </si>
@@ -127,21 +127,12 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>FCX</t>
-  </si>
-  <si>
     <t>COF</t>
   </si>
   <si>
-    <t>FDX</t>
-  </si>
-  <si>
     <t>MRNA</t>
   </si>
   <si>
-    <t>NUE</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -151,36 +142,24 @@
     <t>DFS</t>
   </si>
   <si>
-    <t>MOS</t>
-  </si>
-  <si>
-    <t>BG</t>
-  </si>
-  <si>
-    <t>IVZ</t>
+    <t>GNRC</t>
+  </si>
+  <si>
+    <t>NVDA</t>
   </si>
   <si>
     <t>DVN</t>
   </si>
   <si>
-    <t>STLD</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>GNRC</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
     <t>TGT</t>
   </si>
   <si>
     <t>AMAT</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
     <t>ZBRA</t>
   </si>
   <si>
@@ -190,21 +169,18 @@
     <t>HCA</t>
   </si>
   <si>
-    <t>MS</t>
-  </si>
-  <si>
     <t>TRGP</t>
   </si>
   <si>
-    <t>M</t>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>MV</t>
   </si>
   <si>
     <t>2021-07-22</t>
   </si>
   <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
     <t>2021-08-05</t>
   </si>
   <si>
@@ -217,21 +193,12 @@
     <t>2021-07-21</t>
   </si>
   <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
+    <t>2021-08-18</t>
   </si>
   <si>
     <t>2021-08-03</t>
   </si>
   <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>2021-08-18</t>
-  </si>
-  <si>
     <t>2021-08-19</t>
   </si>
   <si>
@@ -241,73 +208,52 @@
     <t>2021-07-20</t>
   </si>
   <si>
-    <t>2021-07-15</t>
-  </si>
-  <si>
-    <t>Basic Materials</t>
-  </si>
-  <si>
     <t>Financial Services</t>
   </si>
   <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
     <t>Industrials</t>
   </si>
   <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Consumer Cyclical</t>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Energy</t>
   </si>
   <si>
     <t>Consumer Defensive</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Copper</t>
-  </si>
-  <si>
     <t>Credit Services</t>
   </si>
   <si>
-    <t>Integrated Freight &amp; Logistics</t>
-  </si>
-  <si>
     <t>Biotechnology</t>
   </si>
   <si>
-    <t>Steel</t>
-  </si>
-  <si>
     <t>Auto Manufacturers</t>
   </si>
   <si>
-    <t>Agricultural Inputs</t>
-  </si>
-  <si>
-    <t>Farm Products</t>
-  </si>
-  <si>
-    <t>Asset Management</t>
+    <t>Specialty Industrial Machinery</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
   </si>
   <si>
     <t>Oil &amp; Gas E&amp;P</t>
   </si>
   <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>Specialty Industrial Machinery</t>
+    <t>Discount Stores</t>
   </si>
   <si>
     <t>Semiconductor Equipment &amp; Materials</t>
   </si>
   <si>
-    <t>Discount Stores</t>
+    <t>Information Technology Services</t>
   </si>
   <si>
     <t>Communication Equipment</t>
@@ -319,10 +265,10 @@
     <t>Medical Care Facilities</t>
   </si>
   <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
     <t>Oil &amp; Gas Midstream</t>
+  </si>
+  <si>
+    <t>Footwear &amp; Accessories</t>
   </si>
 </sst>
 </file>
@@ -680,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AK17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -801,49 +747,49 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>98.38709677419355</v>
       </c>
       <c r="C2">
-        <v>22</v>
+        <v>186</v>
       </c>
       <c r="D2">
-        <v>41.73</v>
+        <v>157.4</v>
       </c>
       <c r="E2">
-        <v>3.18</v>
+        <v>1.93</v>
       </c>
       <c r="F2">
-        <v>1.000857701832391</v>
+        <v>0.1471906372793176</v>
       </c>
       <c r="G2">
-        <v>3.45</v>
+        <v>1.66</v>
       </c>
       <c r="H2">
-        <v>1.480484890614393</v>
+        <v>-0.7404633467670786</v>
       </c>
       <c r="I2">
-        <v>42.77399978637695</v>
+        <v>155.8779968261719</v>
       </c>
       <c r="J2">
-        <v>42.45850028991699</v>
+        <v>157.7980003356934</v>
       </c>
       <c r="K2">
-        <v>38.64560012817383</v>
+        <v>156.3531994628906</v>
       </c>
       <c r="L2">
-        <v>27.74170004844666</v>
+        <v>115.8003499984741</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="N2">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -852,58 +798,58 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>9.779999999999999</v>
+        <v>57.3</v>
       </c>
       <c r="Y2">
-        <v>46.1</v>
+        <v>168</v>
       </c>
       <c r="Z2">
-        <v>48.64</v>
+        <v>58.54</v>
       </c>
       <c r="AA2">
-        <v>-0.15</v>
+        <v>4.08</v>
       </c>
       <c r="AB2">
-        <v>348</v>
+        <v>425.68</v>
       </c>
       <c r="AC2">
-        <v>1533.33</v>
+        <v>419.46</v>
       </c>
       <c r="AD2">
-        <v>4.87</v>
+        <v>5.44</v>
       </c>
       <c r="AE2">
-        <v>-2</v>
+        <v>30.02</v>
       </c>
       <c r="AF2">
-        <v>127.27</v>
+        <v>7.1</v>
       </c>
       <c r="AG2">
-        <v>633.33</v>
+        <v>329.41</v>
       </c>
       <c r="AH2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="AI2" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="AJ2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="AK2">
-        <v>84.52213439340414</v>
+        <v>83.67676272801762</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -911,49 +857,49 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>94.55645161290323</v>
+        <v>100</v>
       </c>
       <c r="C3">
-        <v>157</v>
+        <v>60</v>
       </c>
       <c r="D3">
-        <v>166.26</v>
+        <v>234.3</v>
       </c>
       <c r="E3">
-        <v>1.31</v>
+        <v>3.37</v>
       </c>
       <c r="F3">
-        <v>-1.345021848893012</v>
+        <v>2.293565499884048</v>
       </c>
       <c r="G3">
-        <v>1.61</v>
+        <v>3.68</v>
       </c>
       <c r="H3">
-        <v>-0.9536301276762481</v>
+        <v>2.125617535569686</v>
       </c>
       <c r="I3">
-        <v>165.0999969482422</v>
+        <v>232.3580017089844</v>
       </c>
       <c r="J3">
-        <v>159.7064987182617</v>
+        <v>216.8935012817383</v>
       </c>
       <c r="K3">
-        <v>146.0553993225098</v>
+        <v>189.7950003051758</v>
       </c>
       <c r="L3">
-        <v>106.9778499412537</v>
+        <v>138.6584001541138</v>
       </c>
       <c r="M3">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -962,58 +908,58 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>3.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
       </c>
       <c r="W3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3">
-        <v>57.3</v>
+        <v>54.21</v>
       </c>
       <c r="Y3">
-        <v>168</v>
+        <v>245.7</v>
       </c>
       <c r="Z3">
-        <v>58.54</v>
+        <v>56.31</v>
       </c>
       <c r="AA3">
-        <v>4.08</v>
+        <v>0.05</v>
       </c>
       <c r="AB3">
-        <v>425.68</v>
+        <v>179.56</v>
       </c>
       <c r="AC3">
-        <v>419.46</v>
+        <v>1083.87</v>
       </c>
       <c r="AD3">
-        <v>5.44</v>
+        <v>31.81</v>
       </c>
       <c r="AE3">
-        <v>30.02</v>
+        <v>529.58</v>
       </c>
       <c r="AF3">
-        <v>7.1</v>
+        <v>-20.34</v>
       </c>
       <c r="AG3">
-        <v>329.41</v>
+        <v>-90.31999999999999</v>
       </c>
       <c r="AH3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="AI3" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="AK3">
-        <v>80.97372377131116</v>
+        <v>79.04004904515946</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1021,43 +967,43 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>95.36290322580645</v>
+        <v>97.37903225806451</v>
       </c>
       <c r="C4">
-        <v>279</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>302.12</v>
+        <v>14.93</v>
       </c>
       <c r="E4">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F4">
-        <v>-1.232118555007832</v>
+        <v>-0.4937407453040392</v>
       </c>
       <c r="G4">
-        <v>1.82</v>
+        <v>2.81</v>
       </c>
       <c r="H4">
-        <v>-0.6758235223278599</v>
+        <v>0.891216363474149</v>
       </c>
       <c r="I4">
-        <v>308.1320007324219</v>
+        <v>14.93400001525879</v>
       </c>
       <c r="J4">
-        <v>308.3879989624023</v>
+        <v>15.08949999809265</v>
       </c>
       <c r="K4">
-        <v>295.5526007080078</v>
+        <v>13.6660000038147</v>
       </c>
       <c r="L4">
-        <v>268.698450012207</v>
+        <v>10.84554996967316</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="N4">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1084,46 +1030,46 @@
         <v>1</v>
       </c>
       <c r="X4">
-        <v>127.29</v>
+        <v>5.74</v>
       </c>
       <c r="Y4">
-        <v>319.9</v>
+        <v>16.45</v>
       </c>
       <c r="Z4">
-        <v>68.72</v>
+        <v>49.2</v>
       </c>
       <c r="AA4">
-        <v>19.24</v>
+        <v>2.76</v>
       </c>
       <c r="AB4">
-        <v>547.27</v>
+        <v>300</v>
       </c>
       <c r="AC4">
-        <v>358.46</v>
+        <v>192.86</v>
       </c>
       <c r="AD4">
-        <v>4.06</v>
+        <v>9.6</v>
       </c>
       <c r="AE4">
-        <v>-27.59</v>
+        <v>217.14</v>
       </c>
       <c r="AF4">
-        <v>-2.32</v>
+        <v>-216.67</v>
       </c>
       <c r="AG4">
-        <v>465.38</v>
+        <v>114.29</v>
       </c>
       <c r="AH4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="AI4" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="AJ4" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="AK4">
-        <v>79.3329072227321</v>
+        <v>69.52309690577171</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1131,43 +1077,43 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>99.59677419354838</v>
+        <v>95.96774193548387</v>
       </c>
       <c r="C5">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D5">
-        <v>206.07</v>
+        <v>58.96</v>
       </c>
       <c r="E5">
-        <v>3.07</v>
+        <v>1.35</v>
       </c>
       <c r="F5">
-        <v>0.8628647870838375</v>
+        <v>-0.7173214601586985</v>
       </c>
       <c r="G5">
-        <v>4.25</v>
+        <v>1.91</v>
       </c>
       <c r="H5">
-        <v>2.538795768132062</v>
+        <v>-0.3857503662798552</v>
       </c>
       <c r="I5">
-        <v>192.5120025634765</v>
+        <v>58.94199981689453</v>
       </c>
       <c r="J5">
-        <v>170.0554992675781</v>
+        <v>60.4329999923706</v>
       </c>
       <c r="K5">
-        <v>160.5943998718262</v>
+        <v>58.7466000366211</v>
       </c>
       <c r="L5">
-        <v>123.4055999183655</v>
+        <v>49.23220002174377</v>
       </c>
       <c r="M5">
-        <v>1.13</v>
+        <v>0.98</v>
       </c>
       <c r="N5">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1185,55 +1131,55 @@
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5">
-        <v>54.21</v>
+        <v>23.33</v>
       </c>
       <c r="Y5">
-        <v>207.38</v>
+        <v>64.3</v>
       </c>
       <c r="Z5">
-        <v>56.31</v>
+        <v>84.12</v>
       </c>
       <c r="AA5">
-        <v>0.05</v>
+        <v>1.67</v>
       </c>
       <c r="AB5">
-        <v>179.56</v>
+        <v>128.94</v>
       </c>
       <c r="AC5">
-        <v>1083.87</v>
+        <v>467.86</v>
       </c>
       <c r="AD5">
-        <v>31.81</v>
+        <v>5.54</v>
       </c>
       <c r="AE5">
-        <v>529.58</v>
+        <v>5.64</v>
       </c>
       <c r="AF5">
-        <v>-20.34</v>
+        <v>-30.36</v>
       </c>
       <c r="AG5">
-        <v>-90.31999999999999</v>
+        <v>600</v>
       </c>
       <c r="AH5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AI5" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="AJ5" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="AK5">
-        <v>73.98225680956961</v>
+        <v>67.03818544957186</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1241,58 +1187,58 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>97.78225806451613</v>
+        <v>97.17741935483872</v>
       </c>
       <c r="C6">
-        <v>112</v>
+        <v>270</v>
       </c>
       <c r="D6">
-        <v>108.78</v>
+        <v>120.2</v>
       </c>
       <c r="E6">
-        <v>3.3</v>
+        <v>1.96</v>
       </c>
       <c r="F6">
-        <v>1.15139542701263</v>
+        <v>0.1919067802502495</v>
       </c>
       <c r="G6">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="H6">
-        <v>0.5544628727864312</v>
+        <v>-0.5418240776942334</v>
       </c>
       <c r="I6">
-        <v>106.831999206543</v>
+        <v>118.8199996948242</v>
       </c>
       <c r="J6">
-        <v>102.7695003509521</v>
+        <v>120.3505004882813</v>
       </c>
       <c r="K6">
-        <v>89.73140014648438</v>
+        <v>117.3674000549316</v>
       </c>
       <c r="L6">
-        <v>62.39909999847412</v>
+        <v>92.24305004119873</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="N6">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>9.444444444444443</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -1301,49 +1247,49 @@
         <v>1</v>
       </c>
       <c r="W6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6">
-        <v>38.51</v>
+        <v>45.4</v>
       </c>
       <c r="Y6">
-        <v>110.97</v>
+        <v>125.38</v>
       </c>
       <c r="Z6">
-        <v>24.28</v>
+        <v>29.16</v>
       </c>
       <c r="AA6">
-        <v>94.33</v>
+        <v>3.98</v>
       </c>
       <c r="AB6">
-        <v>83.67</v>
+        <v>61.93</v>
       </c>
       <c r="AC6">
-        <v>761.11</v>
+        <v>520</v>
       </c>
       <c r="AD6">
-        <v>8.33</v>
+        <v>14.35</v>
       </c>
       <c r="AE6">
-        <v>136.64</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="AF6">
-        <v>107.94</v>
+        <v>6.12</v>
       </c>
       <c r="AG6">
-        <v>75</v>
+        <v>304.17</v>
       </c>
       <c r="AH6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AI6" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="AJ6" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="AK6">
-        <v>72.20263760971538</v>
+        <v>63.3626262102458</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1351,58 +1297,61 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>97.58064516129032</v>
+        <v>99.59677419354838</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>395</v>
       </c>
       <c r="D7">
-        <v>15.97</v>
+        <v>415.2</v>
       </c>
       <c r="E7">
-        <v>3.4</v>
+        <v>1.96</v>
       </c>
       <c r="F7">
-        <v>1.276843531329497</v>
+        <v>0.1919067802502495</v>
       </c>
       <c r="G7">
-        <v>3.04</v>
+        <v>2.49</v>
       </c>
       <c r="H7">
-        <v>0.9381005658865865</v>
+        <v>0.4371837484505034</v>
       </c>
       <c r="I7">
-        <v>15.24200000762939</v>
+        <v>412.6740051269531</v>
       </c>
       <c r="J7">
-        <v>13.14549999237061</v>
+        <v>380.7399978637695</v>
       </c>
       <c r="K7">
-        <v>12.54099994659424</v>
+        <v>341.5031982421875</v>
       </c>
       <c r="L7">
-        <v>10.02844996929169</v>
+        <v>277.7633487701416</v>
       </c>
       <c r="M7">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>1.22</v>
+        <v>1.21</v>
+      </c>
+      <c r="O7" t="s">
+        <v>53</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -1414,46 +1363,46 @@
         <v>1</v>
       </c>
       <c r="X7">
-        <v>5.74</v>
+        <v>123.45</v>
       </c>
       <c r="Y7">
-        <v>16.45</v>
+        <v>419</v>
       </c>
       <c r="Z7">
-        <v>49.2</v>
+        <v>20.99</v>
       </c>
       <c r="AA7">
-        <v>2.76</v>
+        <v>83.91</v>
       </c>
       <c r="AB7">
-        <v>300</v>
+        <v>44.75</v>
       </c>
       <c r="AC7">
-        <v>192.86</v>
+        <v>129.81</v>
       </c>
       <c r="AD7">
-        <v>9.6</v>
+        <v>9.84</v>
       </c>
       <c r="AE7">
-        <v>217.14</v>
+        <v>18.32</v>
       </c>
       <c r="AF7">
-        <v>-216.67</v>
+        <v>8.6</v>
       </c>
       <c r="AG7">
-        <v>114.29</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="AH7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="AI7" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="AJ7" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="AK7">
-        <v>67.52209751117712</v>
+        <v>51.85150751564841</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1461,43 +1410,43 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>95.56451612903226</v>
+        <v>93.14516129032258</v>
       </c>
       <c r="C8">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>63.37</v>
+        <v>20.49</v>
       </c>
       <c r="E8">
-        <v>2.24</v>
+        <v>1.74</v>
       </c>
       <c r="F8">
-        <v>-0.1783544787461536</v>
+        <v>-0.1360116015365842</v>
       </c>
       <c r="G8">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="H8">
-        <v>0.02530743402759643</v>
+        <v>0.2243559601581689</v>
       </c>
       <c r="I8">
-        <v>61.08800048828125</v>
+        <v>20.14265022277832</v>
       </c>
       <c r="J8">
-        <v>57.64149990081787</v>
+        <v>18.69594984054566</v>
       </c>
       <c r="K8">
-        <v>57.94620002746582</v>
+        <v>16.54019487380981</v>
       </c>
       <c r="L8">
-        <v>46.21475002288818</v>
+        <v>14.27079874038696</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1506,13 +1455,13 @@
         <v>0</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -1521,49 +1470,49 @@
         <v>1</v>
       </c>
       <c r="W8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8">
-        <v>23.33</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Y8">
-        <v>63.88</v>
+        <v>20.51</v>
       </c>
       <c r="Z8">
-        <v>84.12</v>
+        <v>379.44</v>
       </c>
       <c r="AA8">
-        <v>1.67</v>
+        <v>2188.34</v>
       </c>
       <c r="AB8">
-        <v>128.94</v>
+        <v>33.89</v>
       </c>
       <c r="AC8">
-        <v>467.86</v>
+        <v>208</v>
       </c>
       <c r="AD8">
-        <v>5.54</v>
+        <v>10.18</v>
       </c>
       <c r="AE8">
-        <v>5.64</v>
+        <v>28.98</v>
       </c>
       <c r="AF8">
-        <v>-30.36</v>
+        <v>10.56</v>
       </c>
       <c r="AG8">
-        <v>600</v>
+        <v>116</v>
       </c>
       <c r="AH8" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="AI8" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="AJ8" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AK8">
-        <v>63.826234635064</v>
+        <v>50.67637486786953</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1571,49 +1520,49 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>94.15322580645162</v>
+        <v>98.58870967741935</v>
       </c>
       <c r="C9">
-        <v>269</v>
+        <v>42</v>
       </c>
       <c r="D9">
-        <v>123.38</v>
+        <v>29.23</v>
       </c>
       <c r="E9">
-        <v>1.65</v>
+        <v>2.98</v>
       </c>
       <c r="F9">
-        <v>-0.9184982942156661</v>
+        <v>1.712255641261933</v>
       </c>
       <c r="G9">
-        <v>1.76</v>
+        <v>3.36</v>
       </c>
       <c r="H9">
-        <v>-0.7551968381416851</v>
+        <v>1.67158492054604</v>
       </c>
       <c r="I9">
-        <v>121.0259994506836</v>
+        <v>28.96199989318848</v>
       </c>
       <c r="J9">
-        <v>117.0309997558594</v>
+        <v>29.14550008773804</v>
       </c>
       <c r="K9">
-        <v>108.6651997375488</v>
+        <v>27.132200050354</v>
       </c>
       <c r="L9">
-        <v>85.60755001068115</v>
+        <v>19.14795001983643</v>
       </c>
       <c r="M9">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="N9">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="P9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1622,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>6.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -1631,49 +1580,49 @@
         <v>1</v>
       </c>
       <c r="W9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>45.4</v>
+        <v>7.73</v>
       </c>
       <c r="Y9">
-        <v>123.98</v>
+        <v>31.99</v>
       </c>
       <c r="Z9">
-        <v>29.16</v>
+        <v>14.22</v>
       </c>
       <c r="AA9">
-        <v>3.98</v>
+        <v>0.04</v>
       </c>
       <c r="AB9">
-        <v>61.93</v>
+        <v>70.81</v>
       </c>
       <c r="AC9">
-        <v>520</v>
+        <v>118.54</v>
       </c>
       <c r="AD9">
-        <v>14.35</v>
+        <v>2.55</v>
       </c>
       <c r="AE9">
-        <v>93.84999999999999</v>
+        <v>222.22</v>
       </c>
       <c r="AF9">
-        <v>6.12</v>
+        <v>-8</v>
       </c>
       <c r="AG9">
-        <v>304.17</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="AH9" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="AI9" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="AJ9" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AK9">
-        <v>62.27896315705645</v>
+        <v>46.75851025325473</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1681,40 +1630,40 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>98.58870967741935</v>
+        <v>91.73387096774194</v>
       </c>
       <c r="C10">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="D10">
-        <v>36.04</v>
+        <v>246.58</v>
       </c>
       <c r="E10">
-        <v>2.57</v>
+        <v>0.78</v>
       </c>
       <c r="F10">
-        <v>0.2356242654995052</v>
+        <v>-1.566928176606404</v>
       </c>
       <c r="G10">
-        <v>2.2</v>
+        <v>1.23</v>
       </c>
       <c r="H10">
-        <v>-0.1731258555069665</v>
+        <v>-1.350569673205103</v>
       </c>
       <c r="I10">
-        <v>36.88399963378906</v>
+        <v>242.9800018310547</v>
       </c>
       <c r="J10">
-        <v>35.9870002746582</v>
+        <v>236.2380020141601</v>
       </c>
       <c r="K10">
-        <v>34.18980010986328</v>
+        <v>223.9498010253906</v>
       </c>
       <c r="L10">
-        <v>25.94814998626709</v>
+        <v>189.502751083374</v>
       </c>
       <c r="M10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N10">
         <v>1.08</v>
@@ -1738,52 +1687,52 @@
         <v>0</v>
       </c>
       <c r="V10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10">
-        <v>11.51</v>
+        <v>116.73</v>
       </c>
       <c r="Y10">
-        <v>38.23</v>
+        <v>246.98</v>
       </c>
       <c r="Z10">
-        <v>12.1</v>
+        <v>104.33</v>
       </c>
       <c r="AA10">
-        <v>7.55</v>
+        <v>5.69</v>
       </c>
       <c r="AB10">
-        <v>176.77</v>
+        <v>39.86</v>
       </c>
       <c r="AC10">
-        <v>215.38</v>
+        <v>24.26</v>
       </c>
       <c r="AD10">
-        <v>1.61</v>
+        <v>14.02</v>
       </c>
       <c r="AE10">
-        <v>-81.28</v>
+        <v>52.73</v>
       </c>
       <c r="AF10">
-        <v>11050</v>
+        <v>36.14</v>
       </c>
       <c r="AG10">
-        <v>-115.38</v>
+        <v>-40.24</v>
       </c>
       <c r="AH10" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AI10" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="AJ10" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="AK10">
-        <v>61.94340388351905</v>
+        <v>25.10276612779291</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1791,40 +1740,40 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>94.95967741935483</v>
+        <v>95.36290322580645</v>
       </c>
       <c r="C11">
-        <v>344</v>
+        <v>74</v>
       </c>
       <c r="D11">
-        <v>89.11</v>
+        <v>138.16</v>
       </c>
       <c r="E11">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="F11">
-        <v>-1.119215261122652</v>
+        <v>0.07266373232776441</v>
       </c>
       <c r="G11">
-        <v>1.65</v>
+        <v>2.38</v>
       </c>
       <c r="H11">
-        <v>-0.900714583800365</v>
+        <v>0.2811100370361246</v>
       </c>
       <c r="I11">
-        <v>88.56000061035157</v>
+        <v>140.2839996337891</v>
       </c>
       <c r="J11">
-        <v>88.4009994506836</v>
+        <v>137.2260002136231</v>
       </c>
       <c r="K11">
-        <v>84.70039962768554</v>
+        <v>133.7838006591797</v>
       </c>
       <c r="L11">
-        <v>67.46414995193481</v>
+        <v>103.8348003768921</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
         <v>1.05</v>
@@ -1845,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
@@ -1854,46 +1803,46 @@
         <v>0</v>
       </c>
       <c r="X11">
-        <v>37.82</v>
+        <v>54.15</v>
       </c>
       <c r="Y11">
-        <v>92.38</v>
+        <v>146</v>
       </c>
       <c r="Z11">
-        <v>11.94</v>
+        <v>123.02</v>
       </c>
       <c r="AA11">
-        <v>9.15</v>
+        <v>39.78</v>
       </c>
       <c r="AB11">
-        <v>305.51</v>
+        <v>18.63</v>
       </c>
       <c r="AC11">
-        <v>61.88</v>
+        <v>57.61</v>
       </c>
       <c r="AD11">
-        <v>15.06</v>
+        <v>11.09</v>
       </c>
       <c r="AE11">
-        <v>49.87</v>
+        <v>17.89</v>
       </c>
       <c r="AF11">
-        <v>105.79</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AG11">
-        <v>-47.51</v>
+        <v>34.78</v>
       </c>
       <c r="AH11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AI11" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="AJ11" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AK11">
-        <v>59.46632792098142</v>
+        <v>23.59465770650193</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1901,37 +1850,37 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>99.39516129032258</v>
+        <v>92.13709677419355</v>
       </c>
       <c r="C12">
-        <v>64</v>
+        <v>408</v>
       </c>
       <c r="D12">
-        <v>29.27</v>
+        <v>253.69</v>
       </c>
       <c r="E12">
-        <v>2.66</v>
+        <v>1.26</v>
       </c>
       <c r="F12">
-        <v>0.3485275593846854</v>
+        <v>-0.8514698890714942</v>
       </c>
       <c r="G12">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="H12">
-        <v>-0.120210311631083</v>
+        <v>-0.08779146267058732</v>
       </c>
       <c r="I12">
-        <v>28.56000022888184</v>
+        <v>245.5759979248047</v>
       </c>
       <c r="J12">
-        <v>27.62499980926514</v>
+        <v>237.3754989624023</v>
       </c>
       <c r="K12">
-        <v>26.80159992218018</v>
+        <v>228.6935995483398</v>
       </c>
       <c r="L12">
-        <v>19.4499499797821</v>
+        <v>176.8778002929687</v>
       </c>
       <c r="M12">
         <v>1.03</v>
@@ -1964,46 +1913,46 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>9.25</v>
+        <v>115.86</v>
       </c>
       <c r="Y12">
-        <v>29.49</v>
+        <v>255.31</v>
       </c>
       <c r="Z12">
-        <v>11.72</v>
+        <v>16.27</v>
       </c>
       <c r="AA12">
-        <v>4.63</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="AB12">
-        <v>37.5</v>
+        <v>4.7</v>
       </c>
       <c r="AC12">
-        <v>544.4400000000001</v>
+        <v>200</v>
       </c>
       <c r="AD12">
-        <v>3.37</v>
+        <v>18.41</v>
       </c>
       <c r="AE12">
-        <v>28.89</v>
+        <v>38.81</v>
       </c>
       <c r="AF12">
-        <v>7.14</v>
+        <v>605.26</v>
       </c>
       <c r="AG12">
-        <v>366.67</v>
+        <v>-69.34999999999999</v>
       </c>
       <c r="AH12" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI12" t="s">
         <v>68</v>
       </c>
-      <c r="AI12" t="s">
-        <v>77</v>
-      </c>
       <c r="AJ12" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AK12">
-        <v>50.18639057919296</v>
+        <v>19.30665599426579</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2011,49 +1960,49 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>97.98387096774194</v>
+        <v>92.54032258064517</v>
       </c>
       <c r="C13">
-        <v>26</v>
+        <v>477</v>
       </c>
       <c r="D13">
-        <v>31.66</v>
+        <v>539.9400000000001</v>
       </c>
       <c r="E13">
-        <v>3.87</v>
+        <v>1.31</v>
       </c>
       <c r="F13">
-        <v>1.866449621618769</v>
+        <v>-0.7769429841199411</v>
       </c>
       <c r="G13">
-        <v>3.39</v>
+        <v>1.51</v>
       </c>
       <c r="H13">
-        <v>1.401111574800567</v>
+        <v>-0.9532911350594124</v>
       </c>
       <c r="I13">
-        <v>30.07799987792969</v>
+        <v>532.9280029296875</v>
       </c>
       <c r="J13">
-        <v>26.95999994277954</v>
+        <v>512.57900390625</v>
       </c>
       <c r="K13">
-        <v>24.312200050354</v>
+        <v>499.5580023193359</v>
       </c>
       <c r="L13">
-        <v>17.2591500043869</v>
+        <v>418.7881500244141</v>
       </c>
       <c r="M13">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="N13">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="P13">
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -2062,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>1.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
@@ -2071,49 +2020,49 @@
         <v>1</v>
       </c>
       <c r="W13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>7.73</v>
+        <v>246.83</v>
       </c>
       <c r="Y13">
-        <v>31.81</v>
+        <v>541.26</v>
       </c>
       <c r="Z13">
-        <v>14.22</v>
+        <v>26.18</v>
       </c>
       <c r="AA13">
-        <v>0.04</v>
+        <v>-15.19</v>
       </c>
       <c r="AB13">
-        <v>70.81</v>
+        <v>4.88</v>
       </c>
       <c r="AC13">
-        <v>118.54</v>
+        <v>127.81</v>
       </c>
       <c r="AD13">
-        <v>2.55</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AE13">
-        <v>222.22</v>
+        <v>14.52</v>
       </c>
       <c r="AF13">
-        <v>-8</v>
+        <v>70.64</v>
       </c>
       <c r="AG13">
-        <v>85.95999999999999</v>
+        <v>16.58</v>
       </c>
       <c r="AH13" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="AI13" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="AJ13" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AK13">
-        <v>47.7652948118664</v>
+        <v>15.56090936667181</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2121,58 +2070,58 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>96.9758064516129</v>
+        <v>92.74193548387096</v>
       </c>
       <c r="C14">
-        <v>240</v>
+        <v>87</v>
       </c>
       <c r="D14">
-        <v>64.86</v>
+        <v>48.52</v>
       </c>
       <c r="E14">
-        <v>2.25</v>
+        <v>1.26</v>
       </c>
       <c r="F14">
-        <v>-0.1658096683144672</v>
+        <v>-0.8514698890714942</v>
       </c>
       <c r="G14">
-        <v>2.32</v>
+        <v>1.41</v>
       </c>
       <c r="H14">
-        <v>-0.01437922387931652</v>
+        <v>-1.095176327254302</v>
       </c>
       <c r="I14">
-        <v>63.95200042724609</v>
+        <v>48.49199981689453</v>
       </c>
       <c r="J14">
-        <v>62.9189998626709</v>
+        <v>46.79249992370605</v>
       </c>
       <c r="K14">
-        <v>56.74619987487793</v>
+        <v>45.36620002746582</v>
       </c>
       <c r="L14">
-        <v>41.38839994430542</v>
+        <v>39.51734994888306</v>
       </c>
       <c r="M14">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N14">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="P14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>8.333333333333332</v>
+        <v>0</v>
       </c>
       <c r="U14" t="b">
         <v>0</v>
@@ -2181,49 +2130,49 @@
         <v>1</v>
       </c>
       <c r="W14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>24</v>
+        <v>23.13</v>
       </c>
       <c r="Y14">
-        <v>66.27</v>
+        <v>49.1</v>
       </c>
       <c r="Z14">
-        <v>10.77</v>
+        <v>37.57</v>
       </c>
       <c r="AA14">
-        <v>2609</v>
+        <v>0.21</v>
       </c>
       <c r="AB14">
-        <v>11.21</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AC14">
-        <v>466.67</v>
+        <v>46.67</v>
       </c>
       <c r="AD14">
-        <v>9.6</v>
+        <v>5.75</v>
       </c>
       <c r="AE14">
-        <v>129.21</v>
+        <v>-56.86</v>
       </c>
       <c r="AF14">
-        <v>85.42</v>
+        <v>18.6</v>
       </c>
       <c r="AG14">
-        <v>33.33</v>
+        <v>186.67</v>
       </c>
       <c r="AH14" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="AI14" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="AJ14" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="AK14">
-        <v>43.95216320702402</v>
+        <v>13.84225193459982</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2231,46 +2180,43 @@
         <v>50</v>
       </c>
       <c r="B15">
-        <v>92.54032258064517</v>
+        <v>94.35483870967742</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>324</v>
       </c>
       <c r="D15">
-        <v>17.58</v>
+        <v>214.85</v>
       </c>
       <c r="E15">
-        <v>2.53</v>
+        <v>1.52</v>
       </c>
       <c r="F15">
-        <v>0.1854450237727586</v>
+        <v>-0.4639299833234179</v>
       </c>
       <c r="G15">
-        <v>2.48</v>
+        <v>1.36</v>
       </c>
       <c r="H15">
-        <v>0.1972829516242176</v>
+        <v>-1.166118923351746</v>
       </c>
       <c r="I15">
-        <v>16.76704978942871</v>
+        <v>209.2440032958984</v>
       </c>
       <c r="J15">
-        <v>15.15926241874695</v>
+        <v>208.345499420166</v>
       </c>
       <c r="K15">
-        <v>14.8222749710083</v>
+        <v>207.8413998413086</v>
       </c>
       <c r="L15">
-        <v>13.67942501544952</v>
+        <v>173.0842500305176</v>
       </c>
       <c r="M15">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="N15">
-        <v>1.13</v>
-      </c>
-      <c r="O15" t="s">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -2282,61 +2228,61 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="U15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
       </c>
       <c r="W15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15">
-        <v>8.69</v>
+        <v>92.06</v>
       </c>
       <c r="Y15">
-        <v>17.66</v>
+        <v>217.36</v>
       </c>
       <c r="Z15">
-        <v>379.44</v>
+        <v>64.66</v>
       </c>
       <c r="AA15">
-        <v>2188.34</v>
+        <v>5.27</v>
       </c>
       <c r="AB15">
-        <v>33.89</v>
+        <v>11.76</v>
       </c>
       <c r="AC15">
-        <v>208</v>
+        <v>31.56</v>
       </c>
       <c r="AD15">
-        <v>10.18</v>
+        <v>63.66</v>
       </c>
       <c r="AE15">
-        <v>28.98</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>10.56</v>
+        <v>113.71</v>
       </c>
       <c r="AG15">
-        <v>116</v>
+        <v>-38.44</v>
       </c>
       <c r="AH15" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="AI15" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AK15">
-        <v>43.7062271642231</v>
+        <v>12.63327431691309</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2344,109 +2290,109 @@
         <v>51</v>
       </c>
       <c r="B16">
-        <v>99.19354838709677</v>
+        <v>96.37096774193549</v>
       </c>
       <c r="C16">
-        <v>448</v>
+        <v>275</v>
       </c>
       <c r="D16">
-        <v>327.4</v>
+        <v>44.8</v>
       </c>
       <c r="E16">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="F16">
-        <v>0.3108931280896252</v>
+        <v>1.086229639668887</v>
       </c>
       <c r="G16">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
       <c r="H16">
-        <v>0.5941495306933435</v>
+        <v>0.4939378253284585</v>
       </c>
       <c r="I16">
-        <v>322.9919982910156</v>
+        <v>44.39599990844727</v>
       </c>
       <c r="J16">
-        <v>310.7094985961914</v>
+        <v>45.78299999237061</v>
       </c>
       <c r="K16">
-        <v>318.3075994873047</v>
+        <v>40.91699989318847</v>
       </c>
       <c r="L16">
-        <v>258.1771490478516</v>
+        <v>29.60169994831085</v>
       </c>
       <c r="M16">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="N16">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="P16">
         <v>0</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16">
         <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="U16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="b">
         <v>1</v>
       </c>
       <c r="X16">
-        <v>101.72</v>
+        <v>13.08</v>
       </c>
       <c r="Y16">
-        <v>364</v>
+        <v>49.2</v>
       </c>
       <c r="Z16">
-        <v>20.99</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AA16">
-        <v>83.91</v>
+        <v>44.34</v>
       </c>
       <c r="AB16">
-        <v>44.75</v>
+        <v>110.32</v>
       </c>
       <c r="AC16">
-        <v>129.81</v>
+        <v>157.14</v>
       </c>
       <c r="AD16">
-        <v>9.84</v>
+        <v>4.13</v>
       </c>
       <c r="AE16">
-        <v>18.32</v>
+        <v>1900</v>
       </c>
       <c r="AF16">
-        <v>8.6</v>
+        <v>-118.75</v>
       </c>
       <c r="AG16">
-        <v>78.84999999999999</v>
+        <v>-23.81</v>
       </c>
       <c r="AH16" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="AI16" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="AJ16" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AK16">
-        <v>41.78366057116936</v>
+        <v>59.53367037491065</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2454,46 +2400,46 @@
         <v>52</v>
       </c>
       <c r="B17">
-        <v>96.37096774193549</v>
+        <v>90.92741935483872</v>
       </c>
       <c r="C17">
-        <v>48</v>
+        <v>172</v>
       </c>
       <c r="D17">
-        <v>65.53</v>
+        <v>65.44</v>
       </c>
       <c r="E17">
-        <v>3.09</v>
+        <v>1.94</v>
       </c>
       <c r="F17">
-        <v>0.8879544079472108</v>
+        <v>0.1620960182696282</v>
       </c>
       <c r="G17">
-        <v>2.76</v>
+        <v>2.32</v>
       </c>
       <c r="H17">
-        <v>0.5676917587554018</v>
+        <v>0.195978921719191</v>
       </c>
       <c r="I17">
-        <v>64.77939987182617</v>
+        <v>64.39099960327148</v>
       </c>
       <c r="J17">
-        <v>61.86225032806396</v>
+        <v>58.21199970245361</v>
       </c>
       <c r="K17">
-        <v>62.34118011474609</v>
+        <v>56.8805330657959</v>
       </c>
       <c r="L17">
-        <v>49.17618494987488</v>
+        <v>50.68624155044556</v>
       </c>
       <c r="M17">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="N17">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -2505,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U17" t="b">
         <v>0</v>
@@ -2517,819 +2463,46 @@
         <v>1</v>
       </c>
       <c r="X17">
-        <v>27.45</v>
+        <v>30.7</v>
       </c>
       <c r="Y17">
-        <v>67.38</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="Z17">
-        <v>86.08</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="AA17">
-        <v>110.96</v>
+        <v>444</v>
       </c>
       <c r="AB17">
-        <v>25.1</v>
+        <v>44.34</v>
       </c>
       <c r="AC17">
-        <v>56.46</v>
+        <v>531.91</v>
       </c>
       <c r="AD17">
-        <v>19.93</v>
+        <v>2.32</v>
       </c>
       <c r="AE17">
-        <v>24.34</v>
+        <v>-86.69</v>
       </c>
       <c r="AF17">
-        <v>6.53</v>
+        <v>151.12</v>
       </c>
       <c r="AG17">
-        <v>18.12</v>
+        <v>1391.86</v>
       </c>
       <c r="AH17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AI17" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="AJ17" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="AK17">
-        <v>28.93034486177274</v>
-      </c>
-    </row>
-    <row r="18" spans="1:37">
-      <c r="A18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18">
-        <v>91.12903225806451</v>
-      </c>
-      <c r="C18">
-        <v>162</v>
-      </c>
-      <c r="D18">
-        <v>231.34</v>
-      </c>
-      <c r="E18">
-        <v>1.87</v>
-      </c>
-      <c r="F18">
-        <v>-0.6425124647185596</v>
-      </c>
-      <c r="G18">
-        <v>1.46</v>
-      </c>
-      <c r="H18">
-        <v>-1.152063417210812</v>
-      </c>
-      <c r="I18">
-        <v>228.6179992675781</v>
-      </c>
-      <c r="J18">
-        <v>219.5665000915527</v>
-      </c>
-      <c r="K18">
-        <v>210.908000793457</v>
-      </c>
-      <c r="L18">
-        <v>180.8572010803223</v>
-      </c>
-      <c r="M18">
-        <v>1.04</v>
-      </c>
-      <c r="N18">
-        <v>1.08</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18" t="b">
-        <v>1</v>
-      </c>
-      <c r="V18" t="b">
-        <v>1</v>
-      </c>
-      <c r="W18" t="b">
-        <v>1</v>
-      </c>
-      <c r="X18">
-        <v>114.81</v>
-      </c>
-      <c r="Y18">
-        <v>231.61</v>
-      </c>
-      <c r="Z18">
-        <v>104.33</v>
-      </c>
-      <c r="AA18">
-        <v>5.69</v>
-      </c>
-      <c r="AB18">
-        <v>39.86</v>
-      </c>
-      <c r="AC18">
-        <v>24.26</v>
-      </c>
-      <c r="AD18">
-        <v>14.02</v>
-      </c>
-      <c r="AE18">
-        <v>52.73</v>
-      </c>
-      <c r="AF18">
-        <v>36.14</v>
-      </c>
-      <c r="AG18">
-        <v>-40.24</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>81</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>97</v>
-      </c>
-      <c r="AK18">
-        <v>28.32504396276335</v>
-      </c>
-    </row>
-    <row r="19" spans="1:37">
-      <c r="A19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19">
-        <v>97.37903225806451</v>
-      </c>
-      <c r="C19">
-        <v>67</v>
-      </c>
-      <c r="D19">
-        <v>139.85</v>
-      </c>
-      <c r="E19">
-        <v>3.16</v>
-      </c>
-      <c r="F19">
-        <v>0.9757680809690177</v>
-      </c>
-      <c r="G19">
-        <v>2.87</v>
-      </c>
-      <c r="H19">
-        <v>0.7132095044140818</v>
-      </c>
-      <c r="I19">
-        <v>138.3160034179687</v>
-      </c>
-      <c r="J19">
-        <v>130.4175010681152</v>
-      </c>
-      <c r="K19">
-        <v>132.3854010009766</v>
-      </c>
-      <c r="L19">
-        <v>96.16545038223266</v>
-      </c>
-      <c r="M19">
-        <v>1.06</v>
-      </c>
-      <c r="N19">
-        <v>1.04</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19" t="b">
-        <v>0</v>
-      </c>
-      <c r="V19" t="b">
-        <v>1</v>
-      </c>
-      <c r="W19" t="b">
-        <v>1</v>
-      </c>
-      <c r="X19">
-        <v>54.15</v>
-      </c>
-      <c r="Y19">
-        <v>146</v>
-      </c>
-      <c r="Z19">
-        <v>123.02</v>
-      </c>
-      <c r="AA19">
-        <v>39.78</v>
-      </c>
-      <c r="AB19">
-        <v>18.63</v>
-      </c>
-      <c r="AC19">
-        <v>57.61</v>
-      </c>
-      <c r="AD19">
-        <v>11.09</v>
-      </c>
-      <c r="AE19">
-        <v>17.89</v>
-      </c>
-      <c r="AF19">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="AG19">
-        <v>34.78</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AI19" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>96</v>
-      </c>
-      <c r="AK19">
-        <v>25.6212115480265</v>
-      </c>
-    </row>
-    <row r="20" spans="1:37">
-      <c r="A20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20">
-        <v>92.13709677419355</v>
-      </c>
-      <c r="C20">
-        <v>481</v>
-      </c>
-      <c r="D20">
-        <v>516.5700000000001</v>
-      </c>
-      <c r="E20">
-        <v>1.74</v>
-      </c>
-      <c r="F20">
-        <v>-0.8055950003304861</v>
-      </c>
-      <c r="G20">
-        <v>1.63</v>
-      </c>
-      <c r="H20">
-        <v>-0.9271723557383067</v>
-      </c>
-      <c r="I20">
-        <v>505.4700012207031</v>
-      </c>
-      <c r="J20">
-        <v>492.2095016479492</v>
-      </c>
-      <c r="K20">
-        <v>491.6608001708984</v>
-      </c>
-      <c r="L20">
-        <v>394.5047993469238</v>
-      </c>
-      <c r="M20">
-        <v>1.03</v>
-      </c>
-      <c r="N20">
-        <v>1.03</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20" t="b">
-        <v>1</v>
-      </c>
-      <c r="V20" t="b">
-        <v>1</v>
-      </c>
-      <c r="W20" t="b">
-        <v>1</v>
-      </c>
-      <c r="X20">
-        <v>244.32</v>
-      </c>
-      <c r="Y20">
-        <v>518.66</v>
-      </c>
-      <c r="Z20">
-        <v>26.18</v>
-      </c>
-      <c r="AA20">
-        <v>-15.19</v>
-      </c>
-      <c r="AB20">
-        <v>4.88</v>
-      </c>
-      <c r="AC20">
-        <v>127.81</v>
-      </c>
-      <c r="AD20">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="AE20">
-        <v>14.52</v>
-      </c>
-      <c r="AF20">
-        <v>70.64</v>
-      </c>
-      <c r="AG20">
-        <v>16.58</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>69</v>
-      </c>
-      <c r="AI20" t="s">
-        <v>83</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK20">
-        <v>16.78955701404053</v>
-      </c>
-    </row>
-    <row r="21" spans="1:37">
-      <c r="A21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21">
-        <v>92.94354838709677</v>
-      </c>
-      <c r="C21">
-        <v>107</v>
-      </c>
-      <c r="D21">
-        <v>45.89</v>
-      </c>
-      <c r="E21">
-        <v>1.63</v>
-      </c>
-      <c r="F21">
-        <v>-0.9435879150790394</v>
-      </c>
-      <c r="G21">
-        <v>1.54</v>
-      </c>
-      <c r="H21">
-        <v>-1.046232329459044</v>
-      </c>
-      <c r="I21">
-        <v>46.08999938964844</v>
-      </c>
-      <c r="J21">
-        <v>44.63449993133545</v>
-      </c>
-      <c r="K21">
-        <v>43.70200012207031</v>
-      </c>
-      <c r="L21">
-        <v>37.82644994735718</v>
-      </c>
-      <c r="M21">
-        <v>1.03</v>
-      </c>
-      <c r="N21">
-        <v>1.05</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21" t="b">
-        <v>0</v>
-      </c>
-      <c r="V21" t="b">
-        <v>1</v>
-      </c>
-      <c r="W21" t="b">
-        <v>1</v>
-      </c>
-      <c r="X21">
-        <v>20</v>
-      </c>
-      <c r="Y21">
-        <v>47.09</v>
-      </c>
-      <c r="Z21">
-        <v>37.57</v>
-      </c>
-      <c r="AA21">
-        <v>0.21</v>
-      </c>
-      <c r="AB21">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="AC21">
-        <v>46.67</v>
-      </c>
-      <c r="AD21">
-        <v>5.75</v>
-      </c>
-      <c r="AE21">
-        <v>-56.86</v>
-      </c>
-      <c r="AF21">
-        <v>18.6</v>
-      </c>
-      <c r="AG21">
-        <v>186.67</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI21" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK21">
-        <v>16.6525563051252</v>
-      </c>
-    </row>
-    <row r="22" spans="1:37">
-      <c r="A22" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22">
-        <v>92.33870967741935</v>
-      </c>
-      <c r="C22">
-        <v>325</v>
-      </c>
-      <c r="D22">
-        <v>213.77</v>
-      </c>
-      <c r="E22">
-        <v>1.35</v>
-      </c>
-      <c r="F22">
-        <v>-1.294842607166265</v>
-      </c>
-      <c r="G22">
-        <v>1.33</v>
-      </c>
-      <c r="H22">
-        <v>-1.324038934807433</v>
-      </c>
-      <c r="I22">
-        <v>213.6639984130859</v>
-      </c>
-      <c r="J22">
-        <v>209.6815002441406</v>
-      </c>
-      <c r="K22">
-        <v>200.8470001220703</v>
-      </c>
-      <c r="L22">
-        <v>165.7172500610351</v>
-      </c>
-      <c r="M22">
-        <v>1.02</v>
-      </c>
-      <c r="N22">
-        <v>1.06</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22" t="b">
-        <v>1</v>
-      </c>
-      <c r="V22" t="b">
-        <v>1</v>
-      </c>
-      <c r="W22" t="b">
-        <v>1</v>
-      </c>
-      <c r="X22">
-        <v>91.20999999999999</v>
-      </c>
-      <c r="Y22">
-        <v>217.36</v>
-      </c>
-      <c r="Z22">
-        <v>64.66</v>
-      </c>
-      <c r="AA22">
-        <v>5.27</v>
-      </c>
-      <c r="AB22">
-        <v>11.76</v>
-      </c>
-      <c r="AC22">
-        <v>31.56</v>
-      </c>
-      <c r="AD22">
-        <v>63.66</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>113.71</v>
-      </c>
-      <c r="AG22">
-        <v>-38.44</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI22" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>100</v>
-      </c>
-      <c r="AK22">
-        <v>16.07678200631016</v>
-      </c>
-    </row>
-    <row r="23" spans="1:37">
-      <c r="A23" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23">
-        <v>91.33064516129032</v>
-      </c>
-      <c r="C23">
-        <v>61</v>
-      </c>
-      <c r="D23">
-        <v>93.95999999999999</v>
-      </c>
-      <c r="E23">
-        <v>1.3</v>
-      </c>
-      <c r="F23">
-        <v>-1.357566659324698</v>
-      </c>
-      <c r="G23">
-        <v>1.52</v>
-      </c>
-      <c r="H23">
-        <v>-1.072690101396986</v>
-      </c>
-      <c r="I23">
-        <v>92.62599945068359</v>
-      </c>
-      <c r="J23">
-        <v>88.61149978637695</v>
-      </c>
-      <c r="K23">
-        <v>83.73599975585938</v>
-      </c>
-      <c r="L23">
-        <v>68.26279996871948</v>
-      </c>
-      <c r="M23">
-        <v>1.05</v>
-      </c>
-      <c r="N23">
-        <v>1.11</v>
-      </c>
-      <c r="O23" t="s">
-        <v>60</v>
-      </c>
-      <c r="P23">
-        <v>2</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="U23" t="b">
-        <v>0</v>
-      </c>
-      <c r="V23" t="b">
-        <v>1</v>
-      </c>
-      <c r="W23" t="b">
-        <v>1</v>
-      </c>
-      <c r="X23">
-        <v>44.44</v>
-      </c>
-      <c r="Y23">
-        <v>94.17</v>
-      </c>
-      <c r="Z23">
-        <v>141.19</v>
-      </c>
-      <c r="AA23">
-        <v>16.23</v>
-      </c>
-      <c r="AB23">
-        <v>13.14</v>
-      </c>
-      <c r="AC23">
-        <v>12.12</v>
-      </c>
-      <c r="AD23">
-        <v>4.17</v>
-      </c>
-      <c r="AE23">
-        <v>18.72</v>
-      </c>
-      <c r="AF23">
-        <v>11.31</v>
-      </c>
-      <c r="AG23">
-        <v>-15.15</v>
-      </c>
-      <c r="AH23" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI23" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ23" t="s">
-        <v>101</v>
-      </c>
-      <c r="AK23">
-        <v>11.81760686820715</v>
-      </c>
-    </row>
-    <row r="24" spans="1:37">
-      <c r="A24" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24">
-        <v>93.95161290322581</v>
-      </c>
-      <c r="C24">
-        <v>149</v>
-      </c>
-      <c r="D24">
-        <v>46.26</v>
-      </c>
-      <c r="E24">
-        <v>3.1</v>
-      </c>
-      <c r="F24">
-        <v>0.9004992183788978</v>
-      </c>
-      <c r="G24">
-        <v>2.41</v>
-      </c>
-      <c r="H24">
-        <v>0.1046807498414217</v>
-      </c>
-      <c r="I24">
-        <v>41.35800018310547</v>
-      </c>
-      <c r="J24">
-        <v>38.97600002288819</v>
-      </c>
-      <c r="K24">
-        <v>35.44319995880127</v>
-      </c>
-      <c r="L24">
-        <v>26.69609992980957</v>
-      </c>
-      <c r="M24">
-        <v>1.06</v>
-      </c>
-      <c r="N24">
-        <v>1.17</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24" t="b">
-        <v>0</v>
-      </c>
-      <c r="V24" t="b">
-        <v>1</v>
-      </c>
-      <c r="W24" t="b">
-        <v>0</v>
-      </c>
-      <c r="X24">
-        <v>13.08</v>
-      </c>
-      <c r="Y24">
-        <v>46.46</v>
-      </c>
-      <c r="Z24">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="AA24">
-        <v>44.34</v>
-      </c>
-      <c r="AB24">
-        <v>110.32</v>
-      </c>
-      <c r="AC24">
-        <v>157.14</v>
-      </c>
-      <c r="AD24">
-        <v>4.13</v>
-      </c>
-      <c r="AE24">
-        <v>1900</v>
-      </c>
-      <c r="AF24">
-        <v>-118.75</v>
-      </c>
-      <c r="AG24">
-        <v>-23.81</v>
-      </c>
-      <c r="AH24" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>82</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>102</v>
-      </c>
-      <c r="AK24">
-        <v>53.96209764382179</v>
+        <v>55.6449317838414</v>
       </c>
     </row>
   </sheetData>
